--- a/docs/qc/testcases/UC-EXBOT-light-check/UC-EXBOT-light-check_light-check_testcases_20260715_v5.xlsx
+++ b/docs/qc/testcases/UC-EXBOT-light-check/UC-EXBOT-light-check_light-check_testcases_20260715_v5.xlsx
@@ -15756,7 +15756,7 @@
       </c>
       <c r="F10" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="F11" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="F19" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="F26" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -16566,7 +16566,7 @@
       </c>
       <c r="F38" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="F39" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -16641,7 +16641,7 @@
       </c>
       <c r="F41" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="F44" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="F50" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="F52" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="F96" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18308,7 +18308,7 @@
       </c>
       <c r="F99" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18539,7 @@
       </c>
       <c r="F107" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="F108" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="F109" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="F114" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18764,7 +18764,7 @@
       </c>
       <c r="F115" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="F118" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -18963,7 +18963,7 @@
       </c>
       <c r="F122" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -19043,7 +19043,7 @@
       </c>
       <c r="F125" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="F126" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -19151,7 +19151,7 @@
       </c>
       <c r="F128" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="F130" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -19274,7 +19274,7 @@
       </c>
       <c r="F133" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19392,7 @@
       </c>
       <c r="F137" s="119" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
     </row>
